--- a/playlists_mini_B.xlsx
+++ b/playlists_mini_B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="32">
   <si>
     <t>vintage culture</t>
   </si>
@@ -40,16 +40,13 @@
     <t>3RloA7E4XMItSP4FjMBv3L</t>
   </si>
   <si>
-    <t>cor</t>
+    <t>corr</t>
   </si>
   <si>
     <t>avicci</t>
   </si>
   <si>
     <t>1vCWHaC5f2uS3yhpwWbIA6</t>
-  </si>
-  <si>
-    <t>corr</t>
   </si>
   <si>
     <t>dub</t>
@@ -98,9 +95,6 @@
   </si>
   <si>
     <t>vintage</t>
-  </si>
-  <si>
-    <t>co</t>
   </si>
   <si>
     <t>ilusionise</t>
@@ -164,13 +158,13 @@
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -449,7 +443,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>3</v>
@@ -458,13 +452,13 @@
     <row r="5" ht="36.0" customHeight="1">
       <c r="C5" s="5"/>
       <c r="D5" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>3</v>
@@ -473,10 +467,10 @@
     <row r="6" ht="36.0" customHeight="1">
       <c r="C6" s="5"/>
       <c r="D6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>2</v>
@@ -488,13 +482,13 @@
     <row r="7" ht="36.0" customHeight="1">
       <c r="C7" s="5"/>
       <c r="D7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>3</v>
@@ -502,7 +496,7 @@
     </row>
     <row r="8" ht="36.0" customHeight="1">
       <c r="D8" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -532,13 +526,13 @@
     <row r="10" ht="36.0" customHeight="1">
       <c r="C10" s="5"/>
       <c r="D10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>3</v>
@@ -553,7 +547,7 @@
         <v>8</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>3</v>
@@ -562,10 +556,10 @@
     <row r="12" ht="36.0" customHeight="1">
       <c r="C12" s="5"/>
       <c r="D12" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>6</v>
@@ -583,7 +577,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>3</v>
@@ -592,10 +586,10 @@
     <row r="14" ht="36.0" customHeight="1">
       <c r="C14" s="5"/>
       <c r="D14" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>2</v>
@@ -607,7 +601,7 @@
     <row r="15" ht="36.0" customHeight="1">
       <c r="C15" s="5"/>
       <c r="D15" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>8</v>
@@ -622,10 +616,10 @@
     <row r="16" ht="36.0" customHeight="1">
       <c r="C16" s="5"/>
       <c r="D16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>9</v>
@@ -652,13 +646,13 @@
     <row r="18" ht="36.0" customHeight="1">
       <c r="C18" s="5"/>
       <c r="D18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F18" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>3</v>
@@ -673,7 +667,7 @@
         <v>8</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>3</v>
@@ -682,13 +676,13 @@
     <row r="20" ht="36.0" customHeight="1">
       <c r="C20" s="5"/>
       <c r="D20" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>3</v>
@@ -712,13 +706,13 @@
     <row r="22" ht="36.0" customHeight="1">
       <c r="C22" s="5"/>
       <c r="D22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>3</v>
@@ -727,7 +721,7 @@
     <row r="23" ht="36.0" customHeight="1">
       <c r="C23" s="5"/>
       <c r="D23" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>5</v>
@@ -748,7 +742,7 @@
         <v>8</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>3</v>
@@ -772,13 +766,13 @@
     <row r="26" ht="36.0" customHeight="1">
       <c r="C26" s="5"/>
       <c r="D26" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F26" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>3</v>
@@ -807,8 +801,8 @@
       <c r="E28" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>29</v>
+      <c r="F28" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>3</v>
@@ -832,13 +826,13 @@
     <row r="30" ht="36.0" customHeight="1">
       <c r="C30" s="5"/>
       <c r="D30" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>9</v>
+      <c r="F30" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>3</v>
@@ -847,10 +841,10 @@
     <row r="31" ht="36.0" customHeight="1">
       <c r="C31" s="5"/>
       <c r="D31" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>2</v>
@@ -868,7 +862,7 @@
         <v>8</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>3</v>
@@ -883,7 +877,7 @@
         <v>1</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>3</v>
@@ -922,13 +916,13 @@
     <row r="36" ht="36.0" customHeight="1">
       <c r="C36" s="5"/>
       <c r="D36" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>3</v>
@@ -937,13 +931,13 @@
     <row r="37" ht="36.0" customHeight="1">
       <c r="C37" s="5"/>
       <c r="D37" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>3</v>
@@ -952,13 +946,13 @@
     <row r="38" ht="36.0" customHeight="1">
       <c r="C38" s="5"/>
       <c r="D38" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>14</v>
+      <c r="F38" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>3</v>
@@ -1012,13 +1006,13 @@
     <row r="42" ht="36.0" customHeight="1">
       <c r="C42" s="5"/>
       <c r="D42" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>3</v>
@@ -1042,13 +1036,13 @@
     <row r="44" ht="36.0" customHeight="1">
       <c r="C44" s="5"/>
       <c r="D44" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>3</v>
@@ -1063,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>3</v>
@@ -1072,10 +1066,10 @@
     <row r="46" ht="36.0" customHeight="1">
       <c r="C46" s="5"/>
       <c r="D46" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>6</v>
@@ -1087,7 +1081,7 @@
     <row r="47" ht="36.0" customHeight="1">
       <c r="C47" s="5"/>
       <c r="D47" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>5</v>
@@ -1108,7 +1102,7 @@
         <v>11</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>3</v>
@@ -1123,7 +1117,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>3</v>
@@ -1132,10 +1126,10 @@
     <row r="50" ht="36.0" customHeight="1">
       <c r="C50" s="5"/>
       <c r="D50" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>2</v>
@@ -1168,7 +1162,7 @@
         <v>5</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>3</v>
@@ -1182,8 +1176,8 @@
       <c r="E53" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F53" s="4" t="s">
-        <v>29</v>
+      <c r="F53" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>3</v>
@@ -1192,7 +1186,7 @@
     <row r="54" ht="36.0" customHeight="1">
       <c r="C54" s="5"/>
       <c r="D54" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>8</v>
@@ -1237,13 +1231,13 @@
     <row r="57" ht="36.0" customHeight="1">
       <c r="C57" s="5"/>
       <c r="D57" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>3</v>
@@ -1252,13 +1246,13 @@
     <row r="58" ht="36.0" customHeight="1">
       <c r="C58" s="5"/>
       <c r="D58" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>9</v>
+      <c r="F58" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>3</v>
@@ -1267,7 +1261,7 @@
     <row r="59" ht="36.0" customHeight="1">
       <c r="C59" s="5"/>
       <c r="D59" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>5</v>
@@ -1282,10 +1276,10 @@
     <row r="60" ht="36.0" customHeight="1">
       <c r="C60" s="5"/>
       <c r="D60" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>6</v>
@@ -1312,13 +1306,13 @@
     <row r="62" ht="36.0" customHeight="1">
       <c r="C62" s="5"/>
       <c r="D62" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>3</v>
@@ -1347,8 +1341,8 @@
       <c r="E64" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F64" s="4" t="s">
-        <v>9</v>
+      <c r="F64" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>3</v>
@@ -1357,7 +1351,7 @@
     <row r="65" ht="36.0" customHeight="1">
       <c r="C65" s="5"/>
       <c r="D65" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>1</v>
@@ -1372,13 +1366,13 @@
     <row r="66" ht="36.0" customHeight="1">
       <c r="C66" s="5"/>
       <c r="D66" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F66" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>3</v>
@@ -1402,10 +1396,10 @@
     <row r="68" ht="36.0" customHeight="1">
       <c r="C68" s="5"/>
       <c r="D68" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>6</v>
@@ -1423,7 +1417,7 @@
         <v>1</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>3</v>
@@ -1432,10 +1426,10 @@
     <row r="70" ht="36.0" customHeight="1">
       <c r="C70" s="5"/>
       <c r="D70" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>2</v>
@@ -1453,7 +1447,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>3</v>
@@ -1492,13 +1486,13 @@
     <row r="74" ht="36.0" customHeight="1">
       <c r="C74" s="5"/>
       <c r="D74" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="F74" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>3</v>
@@ -1527,8 +1521,8 @@
       <c r="E76" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F76" s="4" t="s">
-        <v>9</v>
+      <c r="F76" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>3</v>
@@ -1552,10 +1546,10 @@
     <row r="78" ht="36.0" customHeight="1">
       <c r="C78" s="5"/>
       <c r="D78" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>6</v>
@@ -1567,13 +1561,13 @@
     <row r="79" ht="36.0" customHeight="1">
       <c r="C79" s="5"/>
       <c r="D79" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>3</v>
@@ -1597,13 +1591,13 @@
     <row r="81" ht="36.0" customHeight="1">
       <c r="C81" s="5"/>
       <c r="D81" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F81" s="4" t="s">
-        <v>9</v>
+      <c r="F81" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>3</v>
@@ -1612,13 +1606,13 @@
     <row r="82" ht="36.0" customHeight="1">
       <c r="C82" s="5"/>
       <c r="D82" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E82" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F82" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>3</v>
@@ -1642,13 +1636,13 @@
     <row r="84" ht="36.0" customHeight="1">
       <c r="C84" s="5"/>
       <c r="D84" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F84" s="4" t="s">
-        <v>9</v>
+      <c r="F84" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>3</v>
@@ -1672,13 +1666,13 @@
     <row r="86" ht="36.0" customHeight="1">
       <c r="C86" s="5"/>
       <c r="D86" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>3</v>
@@ -1687,10 +1681,10 @@
     <row r="87" ht="36.0" customHeight="1">
       <c r="C87" s="5"/>
       <c r="D87" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>6</v>
@@ -1722,8 +1716,8 @@
       <c r="E89" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F89" s="4" t="s">
-        <v>9</v>
+      <c r="F89" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>3</v>
@@ -1738,7 +1732,7 @@
         <v>11</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>3</v>
@@ -1762,13 +1756,13 @@
     <row r="92" ht="36.0" customHeight="1">
       <c r="C92" s="5"/>
       <c r="D92" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>3</v>
@@ -1792,13 +1786,13 @@
     <row r="94" ht="36.0" customHeight="1">
       <c r="C94" s="5"/>
       <c r="D94" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>3</v>
@@ -1807,13 +1801,13 @@
     <row r="95" ht="36.0" customHeight="1">
       <c r="C95" s="5"/>
       <c r="D95" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F95" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>3</v>
@@ -1843,7 +1837,7 @@
         <v>1</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>3</v>
@@ -1852,7 +1846,7 @@
     <row r="98" ht="36.0" customHeight="1">
       <c r="C98" s="5"/>
       <c r="D98" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>5</v>
@@ -1873,7 +1867,7 @@
         <v>8</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>3</v>
@@ -1882,10 +1876,10 @@
     <row r="100" ht="36.0" customHeight="1">
       <c r="C100" s="5"/>
       <c r="D100" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>2</v>
@@ -1912,10 +1906,10 @@
     <row r="102" ht="36.0" customHeight="1">
       <c r="C102" s="5"/>
       <c r="D102" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>6</v>
@@ -1927,13 +1921,13 @@
     <row r="103" ht="36.0" customHeight="1">
       <c r="C103" s="5"/>
       <c r="D103" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F103" s="4" t="s">
-        <v>9</v>
+      <c r="F103" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>3</v>
@@ -1948,7 +1942,7 @@
         <v>11</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>3</v>
@@ -1963,7 +1957,7 @@
         <v>1</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>3</v>
@@ -1972,10 +1966,10 @@
     <row r="106" ht="36.0" customHeight="1">
       <c r="C106" s="5"/>
       <c r="D106" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E106" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>2</v>
@@ -1993,7 +1987,7 @@
         <v>8</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>3</v>
@@ -2002,10 +1996,10 @@
     <row r="108" ht="36.0" customHeight="1">
       <c r="C108" s="5"/>
       <c r="D108" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>2</v>
@@ -2032,13 +2026,13 @@
     <row r="110" ht="36.0" customHeight="1">
       <c r="C110" s="5"/>
       <c r="D110" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>3</v>
@@ -2047,13 +2041,13 @@
     <row r="111" ht="36.0" customHeight="1">
       <c r="C111" s="5"/>
       <c r="D111" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>3</v>
@@ -2077,13 +2071,13 @@
     <row r="113" ht="36.0" customHeight="1">
       <c r="C113" s="5"/>
       <c r="D113" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>3</v>
@@ -2092,10 +2086,10 @@
     <row r="114" ht="36.0" customHeight="1">
       <c r="C114" s="5"/>
       <c r="D114" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E114" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>2</v>
@@ -2127,8 +2121,8 @@
       <c r="E116" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F116" s="4" t="s">
-        <v>9</v>
+      <c r="F116" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>3</v>
@@ -2137,7 +2131,7 @@
     <row r="117" ht="36.0" customHeight="1">
       <c r="C117" s="5"/>
       <c r="D117" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>5</v>
@@ -2152,13 +2146,13 @@
     <row r="118" ht="36.0" customHeight="1">
       <c r="C118" s="5"/>
       <c r="D118" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>3</v>
@@ -2173,7 +2167,7 @@
         <v>11</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>3</v>
@@ -2188,7 +2182,7 @@
         <v>8</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>3</v>
@@ -2212,13 +2206,13 @@
     <row r="122" ht="36.0" customHeight="1">
       <c r="C122" s="5"/>
       <c r="D122" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E122" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E122" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="F122" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>3</v>
@@ -2227,7 +2221,7 @@
     <row r="123" ht="36.0" customHeight="1">
       <c r="C123" s="5"/>
       <c r="D123" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>8</v>
@@ -2242,13 +2236,13 @@
     <row r="124" ht="36.0" customHeight="1">
       <c r="C124" s="5"/>
       <c r="D124" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>3</v>
@@ -2272,13 +2266,13 @@
     <row r="126" ht="36.0" customHeight="1">
       <c r="C126" s="5"/>
       <c r="D126" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>3</v>
@@ -2287,10 +2281,10 @@
     <row r="127" ht="36.0" customHeight="1">
       <c r="C127" s="5"/>
       <c r="D127" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>2</v>
@@ -2307,8 +2301,8 @@
       <c r="E128" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F128" s="4" t="s">
-        <v>29</v>
+      <c r="F128" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>3</v>
@@ -2337,8 +2331,8 @@
       <c r="E130" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F130" s="4" t="s">
-        <v>9</v>
+      <c r="F130" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>3</v>
@@ -2362,13 +2356,13 @@
     <row r="132" ht="36.0" customHeight="1">
       <c r="C132" s="5"/>
       <c r="D132" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>3</v>
@@ -2383,7 +2377,7 @@
         <v>1</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>3</v>
@@ -2392,10 +2386,10 @@
     <row r="134" ht="36.0" customHeight="1">
       <c r="C134" s="5"/>
       <c r="D134" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>2</v>
@@ -2407,7 +2401,7 @@
     <row r="135" ht="36.0" customHeight="1">
       <c r="C135" s="5"/>
       <c r="D135" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>5</v>
@@ -2428,7 +2422,7 @@
         <v>8</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>3</v>
@@ -2443,7 +2437,7 @@
         <v>1</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>3</v>
@@ -2452,13 +2446,13 @@
     <row r="138" ht="36.0" customHeight="1">
       <c r="C138" s="5"/>
       <c r="D138" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E138" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E138" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="F138" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>3</v>
@@ -2467,13 +2461,13 @@
     <row r="139" ht="36.0" customHeight="1">
       <c r="C139" s="5"/>
       <c r="D139" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F139" s="4" t="s">
-        <v>9</v>
+      <c r="F139" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>3</v>
@@ -2482,10 +2476,10 @@
     <row r="140" ht="36.0" customHeight="1">
       <c r="C140" s="5"/>
       <c r="D140" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>6</v>
@@ -2512,13 +2506,13 @@
     <row r="142" ht="36.0" customHeight="1">
       <c r="C142" s="5"/>
       <c r="D142" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>3</v>
@@ -2548,7 +2542,7 @@
         <v>8</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>3</v>
@@ -2563,7 +2557,7 @@
         <v>11</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>3</v>
@@ -2572,10 +2566,10 @@
     <row r="146" ht="36.0" customHeight="1">
       <c r="C146" s="5"/>
       <c r="D146" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E146" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>6</v>
@@ -2587,7 +2581,7 @@
     <row r="147" ht="36.0" customHeight="1">
       <c r="C147" s="5"/>
       <c r="D147" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>5</v>
@@ -2602,13 +2596,13 @@
     <row r="148" ht="36.0" customHeight="1">
       <c r="C148" s="5"/>
       <c r="D148" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>3</v>
@@ -2623,7 +2617,7 @@
         <v>1</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>3</v>
@@ -2632,10 +2626,10 @@
     <row r="150" ht="36.0" customHeight="1">
       <c r="C150" s="5"/>
       <c r="D150" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>2</v>
@@ -2647,10 +2641,10 @@
     <row r="151" ht="36.0" customHeight="1">
       <c r="C151" s="5"/>
       <c r="D151" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E151" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>6</v>
@@ -2668,7 +2662,7 @@
         <v>8</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G152" s="2" t="s">
         <v>3</v>
@@ -2677,13 +2671,13 @@
     <row r="153" ht="36.0" customHeight="1">
       <c r="C153" s="5"/>
       <c r="D153" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F153" s="4" t="s">
-        <v>29</v>
+        <v>15</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>3</v>
@@ -2692,10 +2686,10 @@
     <row r="154" ht="36.0" customHeight="1">
       <c r="C154" s="5"/>
       <c r="D154" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E154" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>2</v>
@@ -2707,7 +2701,7 @@
     <row r="155" ht="36.0" customHeight="1">
       <c r="C155" s="5"/>
       <c r="D155" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>8</v>
@@ -2722,10 +2716,10 @@
     <row r="156" ht="36.0" customHeight="1">
       <c r="C156" s="5"/>
       <c r="D156" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>2</v>
@@ -2743,7 +2737,7 @@
         <v>1</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G157" s="2" t="s">
         <v>3</v>
@@ -2752,13 +2746,13 @@
     <row r="158" ht="36.0" customHeight="1">
       <c r="C158" s="5"/>
       <c r="D158" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F158" s="4" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G158" s="2" t="s">
         <v>3</v>
@@ -2812,13 +2806,13 @@
     <row r="162" ht="36.0" customHeight="1">
       <c r="C162" s="5"/>
       <c r="D162" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>3</v>
@@ -2842,13 +2836,13 @@
     <row r="164" ht="36.0" customHeight="1">
       <c r="C164" s="5"/>
       <c r="D164" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F164" s="4" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>3</v>
@@ -2857,7 +2851,7 @@
     <row r="165" ht="36.0" customHeight="1">
       <c r="C165" s="5"/>
       <c r="D165" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>1</v>
@@ -2872,13 +2866,13 @@
     <row r="166" ht="36.0" customHeight="1">
       <c r="C166" s="5"/>
       <c r="D166" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>3</v>
@@ -2887,10 +2881,10 @@
     <row r="167" ht="36.0" customHeight="1">
       <c r="C167" s="5"/>
       <c r="D167" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E167" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>2</v>
@@ -2917,13 +2911,13 @@
     <row r="169" ht="36.0" customHeight="1">
       <c r="C169" s="5"/>
       <c r="D169" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>3</v>
@@ -2953,7 +2947,7 @@
         <v>8</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>3</v>
@@ -2962,10 +2956,10 @@
     <row r="172" ht="36.0" customHeight="1">
       <c r="C172" s="5"/>
       <c r="D172" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>2</v>
@@ -2992,13 +2986,13 @@
     <row r="174" ht="36.0" customHeight="1">
       <c r="C174" s="5"/>
       <c r="D174" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>3</v>
@@ -3027,8 +3021,8 @@
       <c r="E176" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F176" s="4" t="s">
-        <v>9</v>
+      <c r="F176" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>3</v>
@@ -3052,10 +3046,10 @@
     <row r="178" ht="36.0" customHeight="1">
       <c r="C178" s="5"/>
       <c r="D178" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E178" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E178" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>6</v>
@@ -3073,7 +3067,7 @@
         <v>8</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>3</v>
@@ -3082,10 +3076,10 @@
     <row r="180" ht="36.0" customHeight="1">
       <c r="C180" s="5"/>
       <c r="D180" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>2</v>
@@ -3102,8 +3096,8 @@
       <c r="E181" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F181" s="4" t="s">
-        <v>9</v>
+      <c r="F181" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G181" s="2" t="s">
         <v>3</v>
@@ -3112,13 +3106,13 @@
     <row r="182" ht="36.0" customHeight="1">
       <c r="C182" s="5"/>
       <c r="D182" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G182" s="2" t="s">
         <v>3</v>
@@ -3127,10 +3121,10 @@
     <row r="183" ht="36.0" customHeight="1">
       <c r="C183" s="5"/>
       <c r="D183" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E183" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E183" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>2</v>
@@ -3147,8 +3141,8 @@
       <c r="E184" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F184" s="4" t="s">
-        <v>9</v>
+      <c r="F184" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G184" s="2" t="s">
         <v>3</v>
@@ -3172,13 +3166,13 @@
     <row r="186" ht="36.0" customHeight="1">
       <c r="C186" s="5"/>
       <c r="D186" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E186" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E186" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F186" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>3</v>
@@ -3202,10 +3196,10 @@
     <row r="188" ht="36.0" customHeight="1">
       <c r="C188" s="5"/>
       <c r="D188" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>2</v>
@@ -3217,13 +3211,13 @@
     <row r="189" ht="36.0" customHeight="1">
       <c r="C189" s="5"/>
       <c r="D189" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F189" s="4" t="s">
-        <v>9</v>
+      <c r="F189" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>3</v>
@@ -3232,13 +3226,13 @@
     <row r="190" ht="36.0" customHeight="1">
       <c r="C190" s="5"/>
       <c r="D190" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>3</v>
@@ -3247,10 +3241,10 @@
     <row r="191" ht="36.0" customHeight="1">
       <c r="C191" s="5"/>
       <c r="D191" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E191" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E191" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>2</v>
@@ -3292,13 +3286,13 @@
     <row r="194" ht="36.0" customHeight="1">
       <c r="C194" s="5"/>
       <c r="D194" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E194" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E194" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F194" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>3</v>
@@ -3307,13 +3301,13 @@
     <row r="195" ht="36.0" customHeight="1">
       <c r="C195" s="5"/>
       <c r="D195" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>3</v>
@@ -3322,10 +3316,10 @@
     <row r="196" ht="36.0" customHeight="1">
       <c r="C196" s="5"/>
       <c r="D196" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>2</v>
@@ -3343,7 +3337,7 @@
         <v>1</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>3</v>
@@ -3352,10 +3346,10 @@
     <row r="198" ht="36.0" customHeight="1">
       <c r="C198" s="5"/>
       <c r="D198" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>6</v>
@@ -3367,13 +3361,13 @@
     <row r="199" ht="36.0" customHeight="1">
       <c r="C199" s="5"/>
       <c r="D199" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>3</v>
@@ -3432,8 +3426,8 @@
       <c r="E203" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F203" s="4" t="s">
-        <v>9</v>
+      <c r="F203" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>3</v>
@@ -3442,13 +3436,13 @@
     <row r="204" ht="36.0" customHeight="1">
       <c r="C204" s="5"/>
       <c r="D204" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E204" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E204" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="F204" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>3</v>
@@ -3463,7 +3457,7 @@
         <v>1</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>3</v>
@@ -3472,10 +3466,10 @@
     <row r="206" ht="36.0" customHeight="1">
       <c r="C206" s="5"/>
       <c r="D206" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>2</v>
@@ -3487,13 +3481,13 @@
     <row r="207" ht="36.0" customHeight="1">
       <c r="C207" s="5"/>
       <c r="D207" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E207" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E207" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F207" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>3</v>
@@ -3532,13 +3526,13 @@
     <row r="210" ht="36.0" customHeight="1">
       <c r="C210" s="5"/>
       <c r="D210" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>3</v>
@@ -3553,7 +3547,7 @@
         <v>8</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>3</v>
@@ -3562,10 +3556,10 @@
     <row r="212" ht="36.0" customHeight="1">
       <c r="C212" s="5"/>
       <c r="D212" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>6</v>
@@ -3583,7 +3577,7 @@
         <v>1</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>3</v>
@@ -3592,10 +3586,10 @@
     <row r="214" ht="36.0" customHeight="1">
       <c r="C214" s="5"/>
       <c r="D214" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>2</v>
@@ -3627,8 +3621,8 @@
       <c r="E216" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F216" s="4" t="s">
-        <v>9</v>
+      <c r="F216" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>3</v>
@@ -3652,13 +3646,13 @@
     <row r="218" ht="36.0" customHeight="1">
       <c r="C218" s="5"/>
       <c r="D218" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>3</v>
@@ -3673,7 +3667,7 @@
         <v>8</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>3</v>
@@ -3682,13 +3676,13 @@
     <row r="220" ht="36.0" customHeight="1">
       <c r="C220" s="5"/>
       <c r="D220" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>3</v>
@@ -3712,13 +3706,13 @@
     <row r="222" ht="36.0" customHeight="1">
       <c r="C222" s="5"/>
       <c r="D222" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>3</v>
@@ -3727,10 +3721,10 @@
     <row r="223" ht="36.0" customHeight="1">
       <c r="C223" s="5"/>
       <c r="D223" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E223" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>2</v>
@@ -3748,7 +3742,7 @@
         <v>8</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>3</v>
@@ -3772,13 +3766,13 @@
     <row r="226" ht="36.0" customHeight="1">
       <c r="C226" s="5"/>
       <c r="D226" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E226" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E226" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F226" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G226" s="2" t="s">
         <v>3</v>
@@ -3787,7 +3781,7 @@
     <row r="227" ht="36.0" customHeight="1">
       <c r="C227" s="5"/>
       <c r="D227" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>5</v>
@@ -3802,13 +3796,13 @@
     <row r="228" ht="36.0" customHeight="1">
       <c r="C228" s="5"/>
       <c r="D228" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F228" s="4" t="s">
-        <v>29</v>
+        <v>15</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G228" s="2" t="s">
         <v>3</v>
@@ -3832,13 +3826,13 @@
     <row r="230" ht="36.0" customHeight="1">
       <c r="C230" s="5"/>
       <c r="D230" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F230" s="4" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G230" s="2" t="s">
         <v>3</v>
@@ -3847,10 +3841,10 @@
     <row r="231" ht="36.0" customHeight="1">
       <c r="C231" s="5"/>
       <c r="D231" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E231" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>6</v>
@@ -3868,7 +3862,7 @@
         <v>8</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G232" s="2" t="s">
         <v>3</v>
@@ -3883,7 +3877,7 @@
         <v>1</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G233" s="2" t="s">
         <v>3</v>
@@ -3892,10 +3886,10 @@
     <row r="234" ht="36.0" customHeight="1">
       <c r="C234" s="5"/>
       <c r="D234" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E234" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E234" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>2</v>
@@ -3922,13 +3916,13 @@
     <row r="236" ht="36.0" customHeight="1">
       <c r="C236" s="5"/>
       <c r="D236" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>3</v>
@@ -3943,7 +3937,7 @@
         <v>1</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G237" s="2" t="s">
         <v>3</v>
@@ -3952,13 +3946,13 @@
     <row r="238" ht="36.0" customHeight="1">
       <c r="C238" s="5"/>
       <c r="D238" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G238" s="2" t="s">
         <v>3</v>
@@ -3967,13 +3961,13 @@
     <row r="239" ht="36.0" customHeight="1">
       <c r="C239" s="5"/>
       <c r="D239" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E239" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E239" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F239" s="4" t="s">
-        <v>9</v>
+      <c r="F239" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G239" s="2" t="s">
         <v>3</v>
@@ -4018,7 +4012,7 @@
         <v>5</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>3</v>
@@ -4027,10 +4021,10 @@
     <row r="243" ht="36.0" customHeight="1">
       <c r="C243" s="5"/>
       <c r="D243" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>2</v>
@@ -4042,13 +4036,13 @@
     <row r="244" ht="36.0" customHeight="1">
       <c r="C244" s="5"/>
       <c r="D244" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>3</v>
@@ -4063,7 +4057,7 @@
         <v>1</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G245" s="2" t="s">
         <v>3</v>
@@ -4072,7 +4066,7 @@
     <row r="246" ht="36.0" customHeight="1">
       <c r="C246" s="5"/>
       <c r="D246" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>1</v>
@@ -4108,7 +4102,7 @@
         <v>8</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>3</v>
@@ -4123,7 +4117,7 @@
         <v>1</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>3</v>
@@ -4132,10 +4126,10 @@
     <row r="250" ht="36.0" customHeight="1">
       <c r="C250" s="5"/>
       <c r="D250" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E250" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E250" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>2</v>
@@ -4162,7 +4156,7 @@
     <row r="252" ht="36.0" customHeight="1">
       <c r="C252" s="5"/>
       <c r="D252" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>5</v>
@@ -4177,13 +4171,13 @@
     <row r="253" ht="36.0" customHeight="1">
       <c r="C253" s="5"/>
       <c r="D253" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E253" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E253" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F253" s="4" t="s">
-        <v>29</v>
+      <c r="F253" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G253" s="2" t="s">
         <v>3</v>
@@ -4192,10 +4186,10 @@
     <row r="254" ht="36.0" customHeight="1">
       <c r="C254" s="5"/>
       <c r="D254" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>2</v>
@@ -4207,10 +4201,10 @@
     <row r="255" ht="36.0" customHeight="1">
       <c r="C255" s="5"/>
       <c r="D255" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E255" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E255" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>6</v>
@@ -4243,7 +4237,7 @@
         <v>1</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G257" s="2" t="s">
         <v>3</v>
@@ -4252,13 +4246,13 @@
     <row r="258" ht="36.0" customHeight="1">
       <c r="C258" s="5"/>
       <c r="D258" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E258" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E258" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F258" s="4" t="s">
-        <v>9</v>
+      <c r="F258" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G258" s="2" t="s">
         <v>3</v>
@@ -4282,10 +4276,10 @@
     <row r="260" ht="36.0" customHeight="1">
       <c r="C260" s="5"/>
       <c r="D260" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>6</v>
@@ -4312,13 +4306,13 @@
     <row r="262" ht="36.0" customHeight="1">
       <c r="C262" s="5"/>
       <c r="D262" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F262" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>3</v>
@@ -4342,13 +4336,13 @@
     <row r="264" ht="36.0" customHeight="1">
       <c r="C264" s="5"/>
       <c r="D264" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F264" s="4" t="s">
-        <v>9</v>
+      <c r="F264" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G264" s="2" t="s">
         <v>3</v>
@@ -4372,13 +4366,13 @@
     <row r="266" ht="36.0" customHeight="1">
       <c r="C266" s="5"/>
       <c r="D266" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E266" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E266" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F266" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>3</v>
@@ -4402,10 +4396,10 @@
     <row r="268" ht="36.0" customHeight="1">
       <c r="C268" s="5"/>
       <c r="D268" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>6</v>
@@ -4423,7 +4417,7 @@
         <v>1</v>
       </c>
       <c r="F269" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>3</v>
@@ -4432,10 +4426,10 @@
     <row r="270" ht="36.0" customHeight="1">
       <c r="C270" s="5"/>
       <c r="D270" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>2</v>
@@ -4447,13 +4441,13 @@
     <row r="271" ht="36.0" customHeight="1">
       <c r="C271" s="5"/>
       <c r="D271" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F271" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>3</v>
@@ -4492,13 +4486,13 @@
     <row r="274" ht="36.0" customHeight="1">
       <c r="C274" s="5"/>
       <c r="D274" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E274" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E274" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F274" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>3</v>
@@ -4522,13 +4516,13 @@
     <row r="276" ht="36.0" customHeight="1">
       <c r="C276" s="5"/>
       <c r="D276" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F276" s="4" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="F276" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>3</v>
@@ -4552,10 +4546,10 @@
     <row r="278" ht="36.0" customHeight="1">
       <c r="C278" s="5"/>
       <c r="D278" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>6</v>
@@ -4573,7 +4567,7 @@
         <v>11</v>
       </c>
       <c r="F279" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>3</v>
@@ -4597,13 +4591,13 @@
     <row r="281" ht="36.0" customHeight="1">
       <c r="C281" s="5"/>
       <c r="D281" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F281" s="4" t="s">
-        <v>9</v>
+      <c r="F281" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>3</v>
@@ -4612,13 +4606,13 @@
     <row r="282" ht="36.0" customHeight="1">
       <c r="C282" s="5"/>
       <c r="D282" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E282" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E282" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F282" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>3</v>
@@ -4642,10 +4636,10 @@
     <row r="284" ht="36.0" customHeight="1">
       <c r="C284" s="5"/>
       <c r="D284" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>6</v>
@@ -4672,13 +4666,13 @@
     <row r="286" ht="36.0" customHeight="1">
       <c r="C286" s="5"/>
       <c r="D286" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F286" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>3</v>
@@ -4702,10 +4696,10 @@
     <row r="288" ht="36.0" customHeight="1">
       <c r="C288" s="5"/>
       <c r="D288" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E288" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E288" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>2</v>
@@ -4722,8 +4716,8 @@
       <c r="E289" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F289" s="4" t="s">
-        <v>9</v>
+      <c r="F289" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>3</v>
@@ -4732,13 +4726,13 @@
     <row r="290" ht="36.0" customHeight="1">
       <c r="C290" s="5"/>
       <c r="D290" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F290" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>3</v>
@@ -4762,13 +4756,13 @@
     <row r="292" ht="36.0" customHeight="1">
       <c r="C292" s="5"/>
       <c r="D292" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F292" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>3</v>
@@ -4777,7 +4771,7 @@
     <row r="293" ht="36.0" customHeight="1">
       <c r="C293" s="5"/>
       <c r="D293" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E293" s="2" t="s">
         <v>1</v>
@@ -4798,7 +4792,7 @@
         <v>5</v>
       </c>
       <c r="F294" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>3</v>
@@ -4813,7 +4807,7 @@
         <v>1</v>
       </c>
       <c r="F295" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>3</v>
@@ -4843,7 +4837,7 @@
         <v>8</v>
       </c>
       <c r="F297" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>3</v>
@@ -4852,10 +4846,10 @@
     <row r="298" ht="36.0" customHeight="1">
       <c r="C298" s="5"/>
       <c r="D298" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F298" s="3" t="s">
         <v>6</v>
@@ -4873,7 +4867,7 @@
         <v>1</v>
       </c>
       <c r="F299" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>3</v>
@@ -4882,10 +4876,10 @@
     <row r="300" ht="36.0" customHeight="1">
       <c r="C300" s="5"/>
       <c r="D300" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>2</v>
